--- a/data/trans_orig/Q5406-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19919</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>274192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>286868</t>
+          <t>286840</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>328777</t>
+          <t>328383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>339318</t>
+          <t>339311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>607453</t>
+          <t>607693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>623998</t>
+          <t>623767</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22031</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32464</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>58607</t>
+          <t>58758</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179613</t>
+          <t>179118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196095</t>
+          <t>196319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>285923</t>
+          <t>283612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>309348</t>
+          <t>308530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>471054</t>
+          <t>471616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500233</t>
+          <t>499853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>458908</t>
+          <t>457728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>479717</t>
+          <t>479103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>619463</t>
+          <t>617242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>645162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1086078</t>
+          <t>1087961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1120894</t>
+          <t>1119725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>23974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17574</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>34865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282035</t>
+          <t>281916</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300495</t>
+          <t>300460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332040</t>
+          <t>331437</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>346187</t>
+          <t>346206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>620054</t>
+          <t>619422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642918</t>
+          <t>642938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40003</t>
+          <t>41415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>28728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>56514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>15599</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36600</t>
+          <t>36932</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54636</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51945</t>
+          <t>51004</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>82993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>199928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>224006</t>
+          <t>224590</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300726</t>
+          <t>301824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333022</t>
+          <t>334229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>510469</t>
+          <t>509109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>550204</t>
+          <t>550358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>70478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107561</t>
+          <t>106655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488591</t>
+          <t>487365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>520073</t>
+          <t>519776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>638025</t>
+          <t>640420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>674913</t>
+          <t>676420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1138544</t>
+          <t>1143677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1187332</t>
+          <t>1188050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -4042,12 +4042,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7382</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>325096</t>
+          <t>324315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>333328</t>
+          <t>333353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>365749</t>
+          <t>365531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>375717</t>
+          <t>374945</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>694008</t>
+          <t>695094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>707139</t>
+          <t>707072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>11308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23397</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30535</t>
+          <t>29946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52068</t>
+          <t>52400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>37109</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68725</t>
+          <t>68278</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>224907</t>
+          <t>226732</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242988</t>
+          <t>243574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>333601</t>
+          <t>333347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>364517</t>
+          <t>365673</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567259</t>
+          <t>568969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>603478</t>
+          <t>604030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>76591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>556935</t>
+          <t>555653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574788</t>
+          <t>574168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>704444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736535</t>
+          <t>737223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270660</t>
+          <t>1269943</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1307436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5628</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>362862</t>
+          <t>401530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>357314</t>
+          <t>396255</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>365459</t>
+          <t>404338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>599068</t>
+          <t>428736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>592647</t>
+          <t>423930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>604792</t>
+          <t>432628</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>961930</t>
+          <t>830266</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>954482</t>
+          <t>823672</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>968767</t>
+          <t>835799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367545</t>
+          <t>406412</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607154</t>
+          <t>437889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607154</t>
+          <t>437889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607154</t>
+          <t>437889</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>974699</t>
+          <t>844301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974699</t>
+          <t>844301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>974699</t>
+          <t>844301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23117</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>33086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>22890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>40215</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>48043</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54377</t>
+          <t>58058</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>63985</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53482</t>
+          <t>55827</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75402</t>
+          <t>80483</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>284039</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248881</t>
+          <t>274995</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>263972</t>
+          <t>290604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>356332</t>
+          <t>391234</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345087</t>
+          <t>379447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>367480</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>614352</t>
+          <t>675273</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>601165</t>
+          <t>659368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627666</t>
+          <t>688263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425239</t>
+          <t>463963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707252</t>
+          <t>773275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46585</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>620883</t>
+          <t>685568</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>611514</t>
+          <t>675901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628300</t>
+          <t>693278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>955400</t>
+          <t>819970</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>931358</t>
+          <t>805989</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995333</t>
+          <t>831921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1576283</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1553281</t>
+          <t>1489012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1611627</t>
+          <t>1519932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
